--- a/output/parana/01_base_operacional_limpa.xlsx
+++ b/output/parana/01_base_operacional_limpa.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,104 +433,104 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ajuste</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>allowance</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>funcionario</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>centro_de_custo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>projeto</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>contingencia</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>area</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>mes_ano</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>id_quinzena</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>receita_prevista</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>receita_liquida</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>sigla_sub_area</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ano</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>mes</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>ano_mes_str</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>custo_total</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>desvio_receita</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>desvio_pct</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>atingimento_pct</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>receita_ajustada</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ajuste</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Allowance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Funcionário</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Centro de Custo</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Projeto</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Contingência</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Área</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Mês/Ano</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ID Quinzena</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Receita Prevista</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Receita Líquida</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Sigla da Subarea</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Mês</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Ano-Mês</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Custo Total</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Desvio Receita</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Desvio %</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Atingimento %</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Receita Ajustada</t>
         </is>
       </c>
     </row>
@@ -552,7 +564,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I2" t="n">
@@ -626,7 +638,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I3" t="n">
@@ -700,7 +712,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="H4" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I4" t="n">
@@ -774,7 +786,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="H5" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I5" t="n">
@@ -848,7 +860,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="H6" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I6" t="n">
@@ -922,7 +934,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="H7" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I7" t="n">
@@ -996,7 +1008,7 @@
           <t>SL02</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="H8" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="I8" t="n">
@@ -1070,7 +1082,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H9" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I9" t="n">
@@ -1144,7 +1156,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I10" t="n">
@@ -1218,7 +1230,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I11" t="n">
@@ -1292,7 +1304,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I12" t="n">
@@ -1366,7 +1378,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I13" t="n">
@@ -1440,7 +1452,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="H14" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I14" t="n">
@@ -1514,7 +1526,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H15" s="1" t="n">
+      <c r="H15" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I15" t="n">
@@ -1588,7 +1600,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H16" s="1" t="n">
+      <c r="H16" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I16" t="n">
@@ -1662,7 +1674,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H17" s="1" t="n">
+      <c r="H17" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I17" t="n">
@@ -1736,7 +1748,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="H18" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I18" t="n">
@@ -1810,7 +1822,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="H19" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I19" t="n">
@@ -1884,7 +1896,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="H20" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I20" t="n">
@@ -1958,7 +1970,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H21" s="1" t="n">
+      <c r="H21" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I21" t="n">
@@ -2032,7 +2044,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="H22" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="I22" t="n">
@@ -2106,7 +2118,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H23" s="1" t="n">
+      <c r="H23" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I23" t="n">
@@ -2180,7 +2192,7 @@
           <t>SL01</t>
         </is>
       </c>
-      <c r="H24" s="1" t="n">
+      <c r="H24" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="I24" t="n">
